--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -96,6 +96,234 @@
   </si>
   <si>
     <t>7F2B8</t>
+  </si>
+  <si>
+    <t>ED126</t>
+  </si>
+  <si>
+    <t>BE8CF</t>
+  </si>
+  <si>
+    <t>EC0A6</t>
+  </si>
+  <si>
+    <t>90B77</t>
+  </si>
+  <si>
+    <t>D3187</t>
+  </si>
+  <si>
+    <t>A0057</t>
+  </si>
+  <si>
+    <t>2ECB7</t>
+  </si>
+  <si>
+    <t>83270</t>
+  </si>
+  <si>
+    <t>0101E</t>
+  </si>
+  <si>
+    <t>1D065</t>
+  </si>
+  <si>
+    <t>5F2C9</t>
+  </si>
+  <si>
+    <t>C8D76</t>
+  </si>
+  <si>
+    <t>6846B</t>
+  </si>
+  <si>
+    <t>5BB4D</t>
+  </si>
+  <si>
+    <t>2C211</t>
+  </si>
+  <si>
+    <t>31886</t>
+  </si>
+  <si>
+    <t>55B20</t>
+  </si>
+  <si>
+    <t>3AC73</t>
+  </si>
+  <si>
+    <t>AFF76</t>
+  </si>
+  <si>
+    <t>A6941</t>
+  </si>
+  <si>
+    <t>5DFE2</t>
+  </si>
+  <si>
+    <t>7D2E2</t>
+  </si>
+  <si>
+    <t>4FD13</t>
+  </si>
+  <si>
+    <t>DD97E</t>
+  </si>
+  <si>
+    <t>36B93</t>
+  </si>
+  <si>
+    <t>4BC02</t>
+  </si>
+  <si>
+    <t>998EC</t>
+  </si>
+  <si>
+    <t>AF7D7</t>
+  </si>
+  <si>
+    <t>7908E</t>
+  </si>
+  <si>
+    <t>5B5A5</t>
+  </si>
+  <si>
+    <t>0B78A</t>
+  </si>
+  <si>
+    <t>A3586</t>
+  </si>
+  <si>
+    <t>2F94D</t>
+  </si>
+  <si>
+    <t>F8FB0</t>
+  </si>
+  <si>
+    <t>625CF</t>
+  </si>
+  <si>
+    <t>D1C19</t>
+  </si>
+  <si>
+    <t>7E5DC</t>
+  </si>
+  <si>
+    <t>06A2B</t>
+  </si>
+  <si>
+    <t>73CA1</t>
+  </si>
+  <si>
+    <t>61D7B</t>
+  </si>
+  <si>
+    <t>CD52C</t>
+  </si>
+  <si>
+    <t>16FC7</t>
+  </si>
+  <si>
+    <t>81EE6</t>
+  </si>
+  <si>
+    <t>699F1</t>
+  </si>
+  <si>
+    <t>E9E61</t>
+  </si>
+  <si>
+    <t>6CB45</t>
+  </si>
+  <si>
+    <t>82C97</t>
+  </si>
+  <si>
+    <t>142CD</t>
+  </si>
+  <si>
+    <t>92017</t>
+  </si>
+  <si>
+    <t>DA7DE</t>
+  </si>
+  <si>
+    <t>DFB15</t>
+  </si>
+  <si>
+    <t>71412</t>
+  </si>
+  <si>
+    <t>78685</t>
+  </si>
+  <si>
+    <t>169E7</t>
+  </si>
+  <si>
+    <t>97A44</t>
+  </si>
+  <si>
+    <t>8AD1A</t>
+  </si>
+  <si>
+    <t>3D98E</t>
+  </si>
+  <si>
+    <t>27088</t>
+  </si>
+  <si>
+    <t>A7604</t>
+  </si>
+  <si>
+    <t>23B0F</t>
+  </si>
+  <si>
+    <t>24D0D</t>
+  </si>
+  <si>
+    <t>4FD88</t>
+  </si>
+  <si>
+    <t>4217B</t>
+  </si>
+  <si>
+    <t>EA9F8</t>
+  </si>
+  <si>
+    <t>5006D</t>
+  </si>
+  <si>
+    <t>B1A92</t>
+  </si>
+  <si>
+    <t>24727</t>
+  </si>
+  <si>
+    <t>FCD60</t>
+  </si>
+  <si>
+    <t>274D2</t>
+  </si>
+  <si>
+    <t>43861</t>
+  </si>
+  <si>
+    <t>2DE69</t>
+  </si>
+  <si>
+    <t>4EE76</t>
+  </si>
+  <si>
+    <t>B4BB0</t>
+  </si>
+  <si>
+    <t>3216E</t>
+  </si>
+  <si>
+    <t>45BCF</t>
+  </si>
+  <si>
+    <t>E6771</t>
   </si>
 </sst>
 </file>
@@ -479,7 +707,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -502,7 +730,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>

--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="110">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -324,6 +324,36 @@
   </si>
   <si>
     <t>E6771</t>
+  </si>
+  <si>
+    <t>4E1EE</t>
+  </si>
+  <si>
+    <t>9F453</t>
+  </si>
+  <si>
+    <t>511C3</t>
+  </si>
+  <si>
+    <t>FF01A</t>
+  </si>
+  <si>
+    <t>C5A09</t>
+  </si>
+  <si>
+    <t>CC91E</t>
+  </si>
+  <si>
+    <t>EE5C5</t>
+  </si>
+  <si>
+    <t>E3535</t>
+  </si>
+  <si>
+    <t>B053A</t>
+  </si>
+  <si>
+    <t>121DF</t>
   </si>
 </sst>
 </file>
@@ -707,7 +737,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -730,7 +760,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>

--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>121DF</t>
+  </si>
+  <si>
+    <t>34A8A</t>
+  </si>
+  <si>
+    <t>603A7</t>
   </si>
 </sst>
 </file>
@@ -737,7 +743,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -760,7 +766,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>

--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="116">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -360,6 +360,18 @@
   </si>
   <si>
     <t>603A7</t>
+  </si>
+  <si>
+    <t>C31EE</t>
+  </si>
+  <si>
+    <t>B84DF</t>
+  </si>
+  <si>
+    <t>A974B</t>
+  </si>
+  <si>
+    <t>FDC5E</t>
   </si>
 </sst>
 </file>
@@ -743,7 +755,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -766,7 +778,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>

--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="128">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -372,6 +372,42 @@
   </si>
   <si>
     <t>FDC5E</t>
+  </si>
+  <si>
+    <t>7E140</t>
+  </si>
+  <si>
+    <t>8A24F</t>
+  </si>
+  <si>
+    <t>BD1F6</t>
+  </si>
+  <si>
+    <t>C710F</t>
+  </si>
+  <si>
+    <t>485E8</t>
+  </si>
+  <si>
+    <t>55DF0</t>
+  </si>
+  <si>
+    <t>E96F9</t>
+  </si>
+  <si>
+    <t>9B7CE</t>
+  </si>
+  <si>
+    <t>3A21C</t>
+  </si>
+  <si>
+    <t>66640</t>
+  </si>
+  <si>
+    <t>50667</t>
+  </si>
+  <si>
+    <t>57CB8</t>
   </si>
 </sst>
 </file>
@@ -755,7 +791,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -778,7 +814,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>

--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="164">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -408,6 +408,114 @@
   </si>
   <si>
     <t>57CB8</t>
+  </si>
+  <si>
+    <t>3B91B</t>
+  </si>
+  <si>
+    <t>DFBBA</t>
+  </si>
+  <si>
+    <t>C80C9</t>
+  </si>
+  <si>
+    <t>3795F</t>
+  </si>
+  <si>
+    <t>1809D</t>
+  </si>
+  <si>
+    <t>50B98</t>
+  </si>
+  <si>
+    <t>452D0</t>
+  </si>
+  <si>
+    <t>D1911</t>
+  </si>
+  <si>
+    <t>FB4F1</t>
+  </si>
+  <si>
+    <t>D9907</t>
+  </si>
+  <si>
+    <t>6D9E2</t>
+  </si>
+  <si>
+    <t>FC1BF</t>
+  </si>
+  <si>
+    <t>3945D</t>
+  </si>
+  <si>
+    <t>B53AA</t>
+  </si>
+  <si>
+    <t>B8C7D</t>
+  </si>
+  <si>
+    <t>BF94F</t>
+  </si>
+  <si>
+    <t>32825</t>
+  </si>
+  <si>
+    <t>9D41F</t>
+  </si>
+  <si>
+    <t>D19A6</t>
+  </si>
+  <si>
+    <t>17AC8</t>
+  </si>
+  <si>
+    <t>37A78</t>
+  </si>
+  <si>
+    <t>8D740</t>
+  </si>
+  <si>
+    <t>1C1F9</t>
+  </si>
+  <si>
+    <t>73C21</t>
+  </si>
+  <si>
+    <t>D1B42</t>
+  </si>
+  <si>
+    <t>E8E77</t>
+  </si>
+  <si>
+    <t>FCDC5</t>
+  </si>
+  <si>
+    <t>34EA1</t>
+  </si>
+  <si>
+    <t>13B40</t>
+  </si>
+  <si>
+    <t>C076A</t>
+  </si>
+  <si>
+    <t>61A39</t>
+  </si>
+  <si>
+    <t>AE5A8</t>
+  </si>
+  <si>
+    <t>2E193</t>
+  </si>
+  <si>
+    <t>3C43A</t>
+  </si>
+  <si>
+    <t>E05D1</t>
+  </si>
+  <si>
+    <t>C892D</t>
   </si>
 </sst>
 </file>
@@ -791,7 +899,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -814,7 +922,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>

--- a/ResourcesBD/LmtOrderCreationExcel.xlsx
+++ b/ResourcesBD/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="280">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -516,6 +516,354 @@
   </si>
   <si>
     <t>C892D</t>
+  </si>
+  <si>
+    <t>4AFAC</t>
+  </si>
+  <si>
+    <t>F0A92</t>
+  </si>
+  <si>
+    <t>D8918</t>
+  </si>
+  <si>
+    <t>CA25A</t>
+  </si>
+  <si>
+    <t>B93D7</t>
+  </si>
+  <si>
+    <t>956EE</t>
+  </si>
+  <si>
+    <t>5D38A</t>
+  </si>
+  <si>
+    <t>2493A</t>
+  </si>
+  <si>
+    <t>92FC9</t>
+  </si>
+  <si>
+    <t>80FEB</t>
+  </si>
+  <si>
+    <t>55A53</t>
+  </si>
+  <si>
+    <t>6EFE9</t>
+  </si>
+  <si>
+    <t>6A57B</t>
+  </si>
+  <si>
+    <t>03D85</t>
+  </si>
+  <si>
+    <t>8AEBD</t>
+  </si>
+  <si>
+    <t>30991</t>
+  </si>
+  <si>
+    <t>77133</t>
+  </si>
+  <si>
+    <t>19F67</t>
+  </si>
+  <si>
+    <t>247EF</t>
+  </si>
+  <si>
+    <t>C1378</t>
+  </si>
+  <si>
+    <t>617A2</t>
+  </si>
+  <si>
+    <t>E8755</t>
+  </si>
+  <si>
+    <t>8C47A</t>
+  </si>
+  <si>
+    <t>D6C44</t>
+  </si>
+  <si>
+    <t>F24BF</t>
+  </si>
+  <si>
+    <t>F67B0</t>
+  </si>
+  <si>
+    <t>581E7</t>
+  </si>
+  <si>
+    <t>EB8BD</t>
+  </si>
+  <si>
+    <t>9013A</t>
+  </si>
+  <si>
+    <t>CF592</t>
+  </si>
+  <si>
+    <t>A5D0E</t>
+  </si>
+  <si>
+    <t>046CD</t>
+  </si>
+  <si>
+    <t>970B9</t>
+  </si>
+  <si>
+    <t>CA69A</t>
+  </si>
+  <si>
+    <t>0BE2E</t>
+  </si>
+  <si>
+    <t>F70D6</t>
+  </si>
+  <si>
+    <t>5A7CD</t>
+  </si>
+  <si>
+    <t>2D7DE</t>
+  </si>
+  <si>
+    <t>484E5</t>
+  </si>
+  <si>
+    <t>696BA</t>
+  </si>
+  <si>
+    <t>F9B20</t>
+  </si>
+  <si>
+    <t>41FE8</t>
+  </si>
+  <si>
+    <t>59891</t>
+  </si>
+  <si>
+    <t>1F3BA</t>
+  </si>
+  <si>
+    <t>4E87C</t>
+  </si>
+  <si>
+    <t>CD3BD</t>
+  </si>
+  <si>
+    <t>CEB4B</t>
+  </si>
+  <si>
+    <t>2BBC7</t>
+  </si>
+  <si>
+    <t>A1CC2</t>
+  </si>
+  <si>
+    <t>13DE5</t>
+  </si>
+  <si>
+    <t>77430</t>
+  </si>
+  <si>
+    <t>B56E8</t>
+  </si>
+  <si>
+    <t>8D23C</t>
+  </si>
+  <si>
+    <t>4A37E</t>
+  </si>
+  <si>
+    <t>E2BB9</t>
+  </si>
+  <si>
+    <t>520DC</t>
+  </si>
+  <si>
+    <t>C406B</t>
+  </si>
+  <si>
+    <t>22EB6</t>
+  </si>
+  <si>
+    <t>A70D8</t>
+  </si>
+  <si>
+    <t>DAB14</t>
+  </si>
+  <si>
+    <t>33DDA</t>
+  </si>
+  <si>
+    <t>3756E</t>
+  </si>
+  <si>
+    <t>022B3</t>
+  </si>
+  <si>
+    <t>8EFC3</t>
+  </si>
+  <si>
+    <t>3BC0F</t>
+  </si>
+  <si>
+    <t>091C3</t>
+  </si>
+  <si>
+    <t>795B9</t>
+  </si>
+  <si>
+    <t>AD6BA</t>
+  </si>
+  <si>
+    <t>6A810</t>
+  </si>
+  <si>
+    <t>8ECE2</t>
+  </si>
+  <si>
+    <t>492F9</t>
+  </si>
+  <si>
+    <t>7F930</t>
+  </si>
+  <si>
+    <t>8945D</t>
+  </si>
+  <si>
+    <t>A6432</t>
+  </si>
+  <si>
+    <t>1117A</t>
+  </si>
+  <si>
+    <t>234E6</t>
+  </si>
+  <si>
+    <t>FF44A</t>
+  </si>
+  <si>
+    <t>44A10</t>
+  </si>
+  <si>
+    <t>BD2E9</t>
+  </si>
+  <si>
+    <t>C3DEF</t>
+  </si>
+  <si>
+    <t>D84C9</t>
+  </si>
+  <si>
+    <t>18F31</t>
+  </si>
+  <si>
+    <t>37F85</t>
+  </si>
+  <si>
+    <t>9AB26</t>
+  </si>
+  <si>
+    <t>53D19</t>
+  </si>
+  <si>
+    <t>4F694</t>
+  </si>
+  <si>
+    <t>D48AC</t>
+  </si>
+  <si>
+    <t>394A2</t>
+  </si>
+  <si>
+    <t>74912</t>
+  </si>
+  <si>
+    <t>5DFF4</t>
+  </si>
+  <si>
+    <t>7CFDC</t>
+  </si>
+  <si>
+    <t>08E28</t>
+  </si>
+  <si>
+    <t>D5511</t>
+  </si>
+  <si>
+    <t>151F8</t>
+  </si>
+  <si>
+    <t>69FA4</t>
+  </si>
+  <si>
+    <t>C1633</t>
+  </si>
+  <si>
+    <t>65A33</t>
+  </si>
+  <si>
+    <t>DC3AB</t>
+  </si>
+  <si>
+    <t>8DB48</t>
+  </si>
+  <si>
+    <t>6D544</t>
+  </si>
+  <si>
+    <t>A3F94</t>
+  </si>
+  <si>
+    <t>3A05A</t>
+  </si>
+  <si>
+    <t>6BAFC</t>
+  </si>
+  <si>
+    <t>D5DEE</t>
+  </si>
+  <si>
+    <t>CB428</t>
+  </si>
+  <si>
+    <t>08424</t>
+  </si>
+  <si>
+    <t>7251B</t>
+  </si>
+  <si>
+    <t>F5095</t>
+  </si>
+  <si>
+    <t>1D9BE</t>
+  </si>
+  <si>
+    <t>5DC2D</t>
+  </si>
+  <si>
+    <t>BBDD8</t>
+  </si>
+  <si>
+    <t>364AF</t>
+  </si>
+  <si>
+    <t>D9973</t>
+  </si>
+  <si>
+    <t>E3608</t>
+  </si>
+  <si>
+    <t>AA59F</t>
+  </si>
+  <si>
+    <t>E114E</t>
   </si>
 </sst>
 </file>
@@ -899,7 +1247,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
@@ -922,7 +1270,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>9</v>
